--- a/artfynd/A 52168-2025 artfynd.xlsx
+++ b/artfynd/A 52168-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>488243</v>
       </c>
       <c r="B2" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543959.034108002</v>
+        <v>543959</v>
       </c>
       <c r="R2" t="n">
-        <v>7026780.774310593</v>
+        <v>7026781</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,50 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1875273</v>
+        <v>1871509</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill borgvattnet, Jmt</t>
+          <t>Prästbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543951.8521836682</v>
+        <v>543940</v>
       </c>
       <c r="R3" t="n">
-        <v>7026812.98518124</v>
+        <v>7026761</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1568812</v>
+        <v>1875273</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Prästbodarna, Jmt</t>
+          <t>Lill borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543934.9032140314</v>
+        <v>543952</v>
       </c>
       <c r="R4" t="n">
-        <v>7026803.778043187</v>
+        <v>7026813</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2012-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1871509</v>
+        <v>127011844</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1013,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543940.4355176848</v>
+        <v>543944</v>
       </c>
       <c r="R5" t="n">
-        <v>7026760.774548266</v>
+        <v>7027154</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-09-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,15 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52168-2025 artfynd.xlsx
+++ b/artfynd/A 52168-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/488243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1871509</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1875273</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,8 +1092,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011844</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>